--- a/exports/学生实习赋能计划_可行性论证数据表.xlsx
+++ b/exports/学生实习赋能计划_可行性论证数据表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 人群需求分析" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 商业实习-大厂清单" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 商业实习-科技机器人" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 公益项目与增值服务" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 战略取舍-取消开证明" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 收费标准与定价" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 盈利测算" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 落地实施计划" sheetId="8" state="visible" r:id="rId8"/>
@@ -83,7 +83,7 @@
       <color rgb="001A2A33"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -107,12 +107,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0E8E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00B54A4A"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,6 +118,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C06A2F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E8E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -178,6 +183,15 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,15 +199,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,14 +210,34 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -226,12 +251,12 @@
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -246,24 +271,14 @@
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -393,7 +408,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'00 总览Dashboard'!E15</f>
+              <f>'00 总览Dashboard'!E16</f>
             </strRef>
           </tx>
           <spPr>
@@ -403,12 +418,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'00 总览Dashboard'!$A$16:$A$20</f>
+              <f>'00 总览Dashboard'!$A$17:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'00 总览Dashboard'!$E$16:$E$20</f>
+              <f>'00 总览Dashboard'!$E$17:$E$19</f>
             </numRef>
           </val>
         </ser>
@@ -469,7 +484,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2880000"/>
@@ -779,10 +794,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -806,7 +821,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>高中生 / 大学生 / 毕业生  |  商业实习 × 公益补充  |  可行性论证 V1.0</t>
+          <t>高中生 / 大学生 / 毕业生  |  高价值商业实习 × 就业转化  |  已取消开证明低价档  |  V1.1</t>
         </is>
       </c>
     </row>
@@ -836,7 +851,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>学生实习赋能计划（商业实习 + 公益证明服务）</t>
+          <t>学生实习赋能计划（商业企业课题 + 就业转化）</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -902,7 +917,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>商业线（利润中心）+ 公益线（获客与补充）</t>
+          <t>只做高价值：商业标准 / 商业进阶 / 就业转化（已停售开证明）</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -919,12 +934,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>试点周期</t>
+          <t>已停售</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>6 个月（建议）</t>
+          <t>199 / 699 / 1,680 开证明三档（费用低、成本与风险高）</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -941,12 +956,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>基准情景</t>
+          <t>试点周期</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>年付费 220 人 · 均客单 5,800 元 · 营收约 127.6 万 · 毛利率约 38%</t>
+          <t>6 个月（建议）</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -963,12 +978,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>盈亏平衡</t>
+          <t>基准情景</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>固定成本约 28–35 万/年；基准情景可覆盖并盈余</t>
+          <t>年付费 200 人 · 均客单 8,240 元 · 营收约 164.8 万 · 毛利率约 38%</t>
         </is>
       </c>
       <c r="C11" s="7" t="n"/>
@@ -985,12 +1000,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>配套交付</t>
+          <t>盈亏平衡</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>PPT 方案 + 本 Excel 数据表（清单 / 定价 / 测算 / 计划）</t>
+          <t>固定成本约 28–35 万/年；取消低价档后基准情景更易盈余</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -1004,390 +1019,355 @@
       <c r="K12" s="7" t="n"/>
       <c r="L12" s="7" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>二、产品线收入结构（基准情景）</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>配套交付</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>论证 PPT + 流程专项 PPT + 本 Excel</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>二、产品线收入结构（基准情景 · 已无开证明档）</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>人数占比</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>客单价(元)</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>收入(元)</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>收入占比</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>毛利(元)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>公益基础/增值</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>商业标准(科技/具身)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>5480</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>548000</v>
+      </c>
+      <c r="F17" s="13">
+        <f>E17/SUM($E$17:$E$19)</f>
+        <v/>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>186320</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>商业进阶(上海AI/头部)</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
         <v>0.3</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>66</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>299</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>19734</v>
-      </c>
-      <c r="F16" s="13">
-        <f>E16/SUM($E$16:$E$20)</f>
+      <c r="C18" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>11800</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>708000</v>
+      </c>
+      <c r="F18" s="16">
+        <f>E18/SUM($E$17:$E$19)</f>
         <v/>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>10854</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>公益精品(含推荐信)</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>1680</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>36960</v>
-      </c>
-      <c r="F17" s="16">
-        <f>E17/SUM($E$16:$E$20)</f>
+      <c r="G18" s="15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>297360</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>毕业生就业转化包</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>9800</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>392000</v>
+      </c>
+      <c r="F19" s="13">
+        <f>E19/SUM($E$17:$E$19)</f>
         <v/>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>18480</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>商业标准(科技公司)</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>66</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>5480</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>361680</v>
-      </c>
-      <c r="F18" s="13">
-        <f>E18/SUM($E$16:$E$20)</f>
+      <c r="G19" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>156800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17">
+        <f>SUM(C17:C19)</f>
         <v/>
       </c>
-      <c r="G18" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H18" s="11" t="n">
-        <v>144672</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>商业进阶(大厂通道)</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>44</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>11800</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>519200</v>
-      </c>
-      <c r="F19" s="16">
-        <f>E19/SUM($E$16:$E$20)</f>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17">
+        <f>SUM(E17:E19)</f>
         <v/>
       </c>
-      <c r="G19" s="15" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>181720</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>毕业生就业转化包</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>9800</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>215600</v>
-      </c>
-      <c r="F20" s="13">
-        <f>E20/SUM($E$16:$E$20)</f>
+      <c r="F20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17">
+        <f>SUM(H17:H19)</f>
         <v/>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H20" s="11" t="n">
-        <v>81928</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17">
-        <f>SUM(C16:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17">
-        <f>SUM(E16:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17">
-        <f>SUM(H16:H20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>三、三情景摘要（详见「06 盈利测算」）</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-    </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>情景</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>付费人数</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>均客单(元)</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>营收(万元)</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>毛利(万元)</t>
         </is>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>是否覆盖固定成本</t>
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>临界偏稳</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>8240</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>保守</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>4500</v>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="E42" s="11" t="inlineStr">
-        <is>
-          <t>32%</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>临界/偏紧</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>基准</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="n">
-        <v>220</v>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>127.6</v>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>乐观</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n">
-        <v>360</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>6500</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>234</v>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="B42" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>270</v>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="F44" s="11" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="F42" s="14" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>是，可扩张</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A38:L38"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B13:L13"/>
+    <mergeCell ref="A15:L15"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B11:L11"/>
     <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A14:L14"/>
     <mergeCell ref="B10:L10"/>
-    <mergeCell ref="A40:L40"/>
     <mergeCell ref="B9:L9"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="B8:L8"/>
@@ -1403,7 +1383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1487,439 +1467,483 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>供给</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>签约合作企业（家）</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="13">
         <f>IFERROR(D6/C6,0)</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="11">
         <f>IF(D6=0,"未开始",IF(E6&gt;=1,"达成",IF(E6&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>供给</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>可用导师数（人）</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="13">
         <f>IFERROR(D7/C7,0)</f>
         <v/>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="11">
         <f>IF(D7=0,"未开始",IF(E7&gt;=1,"达成",IF(E7&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>销售</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>付费学员（人）</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="13">
         <f>IFERROR(D8/C8,0)</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <f>IF(D8=0,"未开始",IF(E8&gt;=1,"达成",IF(E8&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>双周</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>销售</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>商业线学员（人）</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>商业标准学员（人）</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="13">
         <f>IFERROR(D9/C9,0)</f>
         <v/>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="11">
         <f>IF(D9=0,"未开始",IF(E9&gt;=1,"达成",IF(E9&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>双周</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>销售</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>公益→商业转化率</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D10" s="30" t="n">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>标准→进阶升级率</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="13">
         <f>IFERROR(D10/C10,0)</f>
         <v/>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="11">
         <f>IF(D10=0,"未开始",IF(E10&gt;=1,"达成",IF(E10&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>双周</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>交付</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>证明出具合规率</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="30" t="n">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>企业课题履约率</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D11" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="13">
         <f>IFERROR(D11/C11,0)</f>
         <v/>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="11">
         <f>IF(D11=0,"未开始",IF(E11&gt;=1,"达成",IF(E11&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>交付</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>课程完成率</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="13">
         <f>IFERROR(D12/C12,0)</f>
         <v/>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="11">
         <f>IF(D12=0,"未开始",IF(E12&gt;=1,"达成",IF(E12&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>财务</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>综合毛利率</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="12" t="n">
         <v>0.35</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="13">
         <f>IFERROR(D13/C13,0)</f>
         <v/>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="11">
         <f>IF(D13=0,"未开始",IF(E13&gt;=1,"达成",IF(E13&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>双周</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>财务</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>退费率（低于为佳）</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="12" t="n">
         <v>0.08</v>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="13">
         <f>IFERROR(D14/C14,0)</f>
         <v/>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="11">
         <f>IF(D14=0,"未开始",IF(E14&gt;=1,"达成",IF(E14&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>双周</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>退费率目标为上限，实际应低于目标</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>合规</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>开证明违规报价次数</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13">
+        <f>IF(D15=0,1,0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>IF(D15=0,"达成","风险")</f>
+        <v/>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>双周</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>目标为 0，出现即违规</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>口碑</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>NPS</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C16" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="16">
-        <f>IFERROR(D15/C15,0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="14">
-        <f>IF(D15=0,"未开始",IF(E15&gt;=1,"达成",IF(E15&gt;=0.7,"进行中","风险")))</f>
-        <v/>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>结果</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>就业/升学正向反馈率</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="16">
+      <c r="E16" s="13">
         <f>IFERROR(D16/C16,0)</f>
         <v/>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="11">
         <f>IF(D16=0,"未开始",IF(E16&gt;=1,"达成",IF(E16&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>结果</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>可复用成功案例数</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="D17" s="29" t="n">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>就业/升学正向反馈率</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D17" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="13">
         <f>IFERROR(D17/C17,0)</f>
         <v/>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="11">
         <f>IF(D17=0,"未开始",IF(E17&gt;=1,"达成",IF(E17&gt;=0.7,"进行中","风险")))</f>
         <v/>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>可复用成功案例数</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="13">
+        <f>IFERROR(D18/C18,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="11">
+        <f>IF(D18=0,"未开始",IF(E18&gt;=1,"达成",IF(E18&gt;=0.7,"进行中","风险")))</f>
+        <v/>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>使用说明</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="42" t="inlineStr">
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="46" t="inlineStr">
         <is>
           <t>• 黄色单元格为实际值录入区；完成率与状态自动计算。</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="42" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t>• 「退费率」目标 8% 为上限：实际填写时应尽量低于 8%；状态公式仍按比值计算，需人工结合解读。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="42" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="46" t="inlineStr">
+        <is>
+          <t>• 「开证明违规报价次数」目标为 0：出现即记为风险，用于防止低价档回流。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="46" t="inlineStr">
         <is>
           <t>• 建议每两周同步 Dashboard 与本表，作为可行性复盘输入。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A22:H22"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6:F17">
+  <conditionalFormatting sqref="F6:F18">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"达成"</formula>
     </cfRule>
@@ -2052,7 +2076,7 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>实习证明、推荐信、项目报告</t>
+          <t>真实企业课题+结业证明+可选推荐信</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
@@ -2067,7 +2091,7 @@
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>0–1,980</t>
+          <t>5,480–11,800</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
@@ -2077,12 +2101,12 @@
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>公益基础→精品</t>
+          <t>商业标准/进阶</t>
         </is>
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>寒暑假 2–8 周</t>
+          <t>不卖开证明；走项目档</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2143,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>3,980–15,800</t>
+          <t>5,480–15,800</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -2249,324 +2273,324 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>高中生</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>海外申请实习证明</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n">
+          <t>海外申请真实课题经历</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>正规渠道少</t>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>缺正规高价值通道</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>上线公益证明版+编号核验</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
+          <t>导入商业标准/进阶项目档</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>高中生</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>推荐信协助</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
+          <t>结业证明与推荐信</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>不可再靠低价开证明</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>仅随项目交付；推荐信加购</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>大学生</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>大厂/上海AI品牌经历</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>模板与导师签字流缺失</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>精品包含模板/润色/签字</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>名额稀缺、信息不对称</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>建立分层企业合作池</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>高中生</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>申报邮箱与材料清单</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>家长操作成本高</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>提供申报通道与清单</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>大学生</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>科技/具身智能硬科技履历</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>学生不知如何进入</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>上海具身智能清单优先签约</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>大厂/500强品牌经历</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>简历与面试辅导</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>分散在其他机构</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>作为项目内增值加购</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>毕业生</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>过渡实习岗位</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>名额稀缺、信息不对称</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>建立分层企业合作池</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>毕业后无人管</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>就业转化包 4–12 周</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr"/>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>大学生</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>科技/机器人硬科技履历</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>学生不知如何进入</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>机器人/AI 公司清单签约</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr"/>
-      <c r="H16" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>毕业生</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>内推与 Offer 转化</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>缺少闭环</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>合作企业内推+复盘</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>大学生</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>简历与面试辅导</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>分散在其他机构</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>作为增值单卖或打包</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr"/>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>毕业生</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>过渡实习岗位</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="n">
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>战略</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>停售开证明低价档</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>毕业后无人管</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>就业转化包 4–12 周</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>费用低风险高</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>199/699/1680 一律停售</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>毕业生</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>内推与 Offer 转化</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
+      <c r="G19" s="11" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>共性</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>真实课题可核验</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>缺少闭环</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>合作企业内推+复盘</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>行业信任危机</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>过程材料留存+企业评语</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr"/>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>共性</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>证明可核验与合规</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>行业信任危机</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>编号系统+抽查机制</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr"/>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr"/>
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
@@ -2699,20 +2723,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>全球科技</t>
         </is>
@@ -2722,27 +2746,27 @@
           <t>产品/数据/工程</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>远程课题+导师营</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>大学生/优生</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="14" t="n">
         <v>4500</v>
       </c>
       <c r="K6" s="19" t="inlineStr">
@@ -2752,20 +2776,20 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>全球科技</t>
         </is>
@@ -2775,46 +2799,46 @@
           <t>云/开发/数据分析</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>远程课题+导师营</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="11" t="n">
         <v>4200</v>
       </c>
       <c r="K7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>全球科技</t>
         </is>
@@ -2824,46 +2848,46 @@
           <t>运营/数据/云</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="14" t="n">
         <v>4000</v>
       </c>
       <c r="K8" s="19" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>全球科技</t>
         </is>
@@ -2873,46 +2897,46 @@
           <t>产品/增长/内容</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>远程课题</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="11" t="n">
         <v>4500</v>
       </c>
       <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>腾讯</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>互联网大厂</t>
         </is>
@@ -2922,27 +2946,27 @@
           <t>产品运营/研发/市场</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>暑期营/项目制</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="14" t="n">
         <v>3500</v>
       </c>
       <c r="K10" s="19" t="inlineStr">
@@ -2952,20 +2976,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>阿里巴巴</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>互联网大厂</t>
         </is>
@@ -2975,46 +2999,46 @@
           <t>电商运营/技术/数据</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="11" t="n">
         <v>3500</v>
       </c>
       <c r="K11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>字节跳动</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>互联网大厂</t>
         </is>
@@ -3024,27 +3048,27 @@
           <t>内容/产品/算法应用</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="14" t="n">
         <v>3800</v>
       </c>
       <c r="K12" s="19" t="inlineStr">
@@ -3054,20 +3078,20 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>美团</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>互联网大厂</t>
         </is>
@@ -3077,46 +3101,46 @@
           <t>本地生活运营/数据</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="11" t="n">
         <v>2800</v>
       </c>
       <c r="K13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>火山引擎</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>云与AI</t>
         </is>
@@ -3126,27 +3150,27 @@
           <t>大模型应用/数据</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>课题实训营</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J14" s="14" t="n">
         <v>3000</v>
       </c>
       <c r="K14" s="19" t="inlineStr">
@@ -3156,20 +3180,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>阿里云</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>云与AI</t>
         </is>
@@ -3179,46 +3203,46 @@
           <t>云原生/解决方案</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>课题实训营</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>理工大学生</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="11" t="n">
         <v>3000</v>
       </c>
       <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>腾讯云</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>云与AI</t>
         </is>
@@ -3228,46 +3252,46 @@
           <t>云与安全</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>课题实训营</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>理工大学生</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="14" t="n">
         <v>3000</v>
       </c>
       <c r="K16" s="19" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>华为云</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>云与AI</t>
         </is>
@@ -3277,46 +3301,46 @@
           <t>云/鸿蒙生态应用</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>课题实训营</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>理工大学生</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="11" t="n">
         <v>3200</v>
       </c>
       <c r="K17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>消费电子</t>
         </is>
@@ -3326,46 +3350,46 @@
           <t>市场/用户研究</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>短期项目实习</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" s="14" t="n">
         <v>2500</v>
       </c>
       <c r="K18" s="19" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>OPPO</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>消费电子</t>
         </is>
@@ -3375,46 +3399,46 @@
           <t>产品市场</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>短期项目实习</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="11" t="n">
         <v>2400</v>
       </c>
       <c r="K19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>消费电子</t>
         </is>
@@ -3424,46 +3448,46 @@
           <t>品牌/用户洞察</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>短期项目实习</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J20" s="14" t="n">
         <v>2400</v>
       </c>
       <c r="K20" s="19" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>综合500强</t>
         </is>
@@ -3473,46 +3497,46 @@
           <t>咨询/数字化</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>校企联合课题</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>大学生/毕业生</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J21" s="14" t="n">
+      <c r="J21" s="11" t="n">
         <v>2200</v>
       </c>
       <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>综合500强</t>
         </is>
@@ -3522,46 +3546,46 @@
           <t>企业软件实施</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>项目助理</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>信息管理/商科</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" s="14" t="n">
         <v>2200</v>
       </c>
       <c r="K22" s="19" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>西门子</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>综合500强</t>
         </is>
@@ -3571,46 +3595,46 @@
           <t>工业数字化</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>课题实习</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J23" s="14" t="n">
+      <c r="J23" s="11" t="n">
         <v>2500</v>
       </c>
       <c r="K23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>联合利华</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>综合500强</t>
         </is>
@@ -3620,46 +3644,46 @@
           <t>品牌/市场</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>商科</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="J24" s="14" t="n">
         <v>2000</v>
       </c>
       <c r="K24" s="19" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>宝洁</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>综合500强</t>
         </is>
@@ -3669,46 +3693,46 @@
           <t>品牌管理</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>商科</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J25" s="14" t="n">
+      <c r="J25" s="11" t="n">
         <v>2200</v>
       </c>
       <c r="K25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>蚂蚁集团</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>金融科技</t>
         </is>
@@ -3718,46 +3742,46 @@
           <t>风控/运营/数据</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>远程项目实习</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>大学生/毕业生</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J26" s="11" t="n">
+      <c r="J26" s="14" t="n">
         <v>3000</v>
       </c>
       <c r="K26" s="19" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>京东科技</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>金融科技</t>
         </is>
@@ -3767,46 +3791,46 @@
           <t>数科产品/运营</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J27" s="14" t="n">
+      <c r="J27" s="11" t="n">
         <v>2600</v>
       </c>
       <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>平安科技</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>金融科技</t>
         </is>
@@ -3816,27 +3840,27 @@
           <t>科技赋能/数据</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>大学生</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J28" s="14" t="n">
         <v>2400</v>
       </c>
       <c r="K28" s="19" t="inlineStr"/>
@@ -3891,96 +3915,96 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>S 级</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>8,800–15,800</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>≤40%</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>大厂/全球科技通道营</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>4–6 周</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>A 级</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>5,980–9,800</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>≤35%</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>云与 AI / 消费电子项目营</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>4 周</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>B 级</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>3,980–6,980</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>≤30%</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>综合 500 强 / 金科项目实习</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>4 周</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
@@ -4116,20 +4140,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>人形/工业机器人</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>优必选</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>理工大学生</t>
         </is>
@@ -4139,46 +4163,46 @@
           <t>算法/机械/测试</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>实岗或课题</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="14" t="n">
         <v>5980</v>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>深圳/混合</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr"/>
+      <c r="K6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>人形/工业机器人</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>宇树科技</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>理工大学生</t>
         </is>
@@ -4188,50 +4212,50 @@
           <t>嵌入式/运动控制</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>课题实训</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="11" t="n">
         <v>6480</v>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>杭州/混合</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>热门，名额紧</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>人形/工业机器人</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>节卡机器人</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>机械/自动化</t>
         </is>
@@ -4241,46 +4265,46 @@
           <t>应用工程师助理</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="14" t="n">
         <v>4980</v>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr"/>
+      <c r="K8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>人形/工业机器人</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>埃斯顿</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>自动化相关</t>
         </is>
@@ -4290,46 +4314,46 @@
           <t>工业机器人应用</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="11" t="n">
         <v>4980</v>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
       </c>
-      <c r="K9" s="14" t="inlineStr"/>
+      <c r="K9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>自动驾驶/出行</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>小马智行</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>计算机/车辆</t>
         </is>
@@ -4339,46 +4363,46 @@
           <t>感知标注/仿真支持</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>远程+驻场</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="14" t="n">
         <v>6800</v>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>广州/远程</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr"/>
+      <c r="K10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>自动驾驶/出行</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>文远知行</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>计算机相关</t>
         </is>
@@ -4388,46 +4412,46 @@
           <t>运营支持/数据</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="11" t="n">
         <v>6500</v>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="K11" s="14" t="inlineStr"/>
+      <c r="K11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>自动驾驶/出行</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Momenta</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>算法相关</t>
         </is>
@@ -4437,46 +4461,46 @@
           <t>数据闭环支持</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>课题</t>
         </is>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="14" t="n">
         <v>6800</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>苏州/远程</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
+      <c r="K12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>具身智能/AI硬件</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>智元机器人</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>硕本交叉</t>
         </is>
@@ -4486,46 +4510,46 @@
           <t>数据采集/应用demo</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>课题营</t>
         </is>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="11" t="n">
         <v>7200</v>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="K13" s="14" t="inlineStr"/>
+      <c r="K13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>具身智能/AI硬件</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>银河通用</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>AI/机器人</t>
         </is>
@@ -4535,46 +4559,46 @@
           <t>具身数据与评测</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>课题</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="14" t="n">
         <v>7000</v>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr"/>
+      <c r="K14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>具身智能/AI硬件</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>云深处科技</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>机械/控制</t>
         </is>
@@ -4584,46 +4608,46 @@
           <t>四足机器人应用</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="11" t="n">
         <v>5800</v>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="K15" s="14" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>企业服务SaaS</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>用友</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>商科/信管</t>
         </is>
@@ -4633,50 +4657,50 @@
           <t>实施助理/客户成功</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="14" t="n">
         <v>3980</v>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>远程/北京</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>易起量</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>企业服务SaaS</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>金蝶</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>商科/信管</t>
         </is>
@@ -4686,46 +4710,46 @@
           <t>实施/支持</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="11" t="n">
         <v>3980</v>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>远程/深圳</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>企业服务SaaS</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>销售易</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>市场营销/信管</t>
         </is>
@@ -4735,46 +4759,46 @@
           <t>售前支持/运营</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>远程实习</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="14" t="n">
         <v>4200</v>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>远程</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr"/>
+      <c r="K18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>企业服务SaaS</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>北森</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>人力/心理/信管</t>
         </is>
@@ -4784,46 +4808,46 @@
           <t>HR SaaS 运营支持</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>远程实习</t>
         </is>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G19" s="11" t="n">
         <v>4200</v>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>远程</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr"/>
+      <c r="K19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>半导体/芯片生态</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>寒武纪</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>电子信息</t>
         </is>
@@ -4833,50 +4857,50 @@
           <t>工具链文档/资料研究</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>课题研究</t>
         </is>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="14" t="n">
         <v>5500</v>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>北京/远程</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K20" s="14" t="inlineStr">
         <is>
           <t>表述需谨慎</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>半导体/芯片生态</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>地平线</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>电子/计算机</t>
         </is>
@@ -4886,46 +4910,46 @@
           <t>嵌入式工具支持</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>课题</t>
         </is>
       </c>
-      <c r="G21" s="14" t="n">
+      <c r="G21" s="11" t="n">
         <v>5800</v>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>上海/远程</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>生物科技/医疗AI</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>联影智能</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>生医/AI交叉</t>
         </is>
@@ -4935,46 +4959,46 @@
           <t>标注/产品助理</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="14" t="n">
         <v>5200</v>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr"/>
+      <c r="K22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>生物科技/医疗AI</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>推想科技</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>生医/AI</t>
         </is>
@@ -4984,46 +5008,46 @@
           <t>文献/数据标注</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>远程项目</t>
         </is>
       </c>
-      <c r="G23" s="14" t="n">
+      <c r="G23" s="11" t="n">
         <v>4800</v>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>远程</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>生物科技/医疗AI</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>数坤科技</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>生医交叉</t>
         </is>
@@ -5033,30 +5057,30 @@
           <t>产品助理支持</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>项目制</t>
         </is>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr"/>
+      <c r="K24" s="14" t="inlineStr"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
@@ -5103,17 +5127,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>企业服务 SaaS</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -5121,24 +5145,24 @@
           <t>合作门槛低、远程友好、易标准化交付</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>商科/综合类大学生</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>人形/工业机器人</t>
         </is>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="14" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="19" t="inlineStr">
@@ -5146,24 +5170,24 @@
           <t>履历辨识度高、家长与学生兴趣强</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>理工大学生</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>具身智能/AI 硬件</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -5171,24 +5195,24 @@
           <t>热点赛道，支撑进阶定价</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>优生/交叉背景</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>医疗 AI</t>
         </is>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" s="14" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="19" t="inlineStr">
@@ -5196,24 +5220,24 @@
           <t>差异化，适合生医交叉</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>相关专业</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>自动驾驶/芯片</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -5221,7 +5245,7 @@
           <t>品牌强但对接周期长</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>对口专业</t>
         </is>
@@ -5249,607 +5273,485 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>公益类实习项目与增值支持</t>
+          <t>战略取舍：取消「开证明」业务</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>线上实习盖证明 · 申报邮箱链接 · 推荐信协助</t>
+          <t>费用低 · 成本与风险高 → 一律停售 199 / 699 / 1,680，聚焦高价值商业与就业档</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>一、公益产品包</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>一、已停售产品（不再报价、不再交付）</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="21" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="21" t="n"/>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>产品代码</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>服务内容</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>交付物</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>周期</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>建议定价(元)</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>成本估算(元)</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>目标毛利率</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>主要人群</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>原产品代码</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>原产品名称</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>原定价(元)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>停售原因</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>替代方案</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>GW-01</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>线上实习·证明版</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>任务平台+周打卡+轻量批改</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>带编号实习证明</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>2–4 周</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="C6" s="23" t="n">
         <v>199</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>高中生/预算敏感大学生</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>客单过低；核验/舆情成本高</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>导入商业标准项目 5,480</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>GW-02</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>证明+申报支持</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>GW-01 + 申报邮箱通道 + 材料清单 + 截止提醒</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>证明+申报进度页</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>2–4 周</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="n">
+      <c r="C7" s="23" t="n">
         <v>699</v>
       </c>
-      <c r="G7" s="14" t="n">
-        <v>220</v>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>高中申请党</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>费用低、运营带宽占用大</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>随项目交付结业证明</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>GW-03</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>证明+推荐信协助</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>GW-02 + 推荐信模板/润色 + 导师签字流</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>证明+中/英文推荐信</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>3–6 周</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="n">
+      <c r="C8" s="23" t="n">
         <v>1680</v>
       </c>
-      <c r="G8" s="11" t="n">
-        <v>720</v>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>海外申请</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>GW-04</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>公益团购(学校)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>批量名额+统一证明模板</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>批量证明</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>按学期</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>按人 6–8 折</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>≥45%</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>B 端学校/机构</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>二、三项补充能力拆解</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>能力模块</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>具体动作</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>系统/工具</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>SLA</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>负责人角色</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>是否收费</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>单独售卖风险高、易被质疑水经历</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>仅项目学员加购 +1,500</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>二、为什么取消（决策依据）</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="26" t="n"/>
+      <c r="I10" s="26" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>客单价</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>199–1,680 元档难以覆盖真实企业对接与合规成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>(a) 线上实习盖证明</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>发布任务、批改、结业审核、编号出具</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>任务平台+证明模板</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>结业后 3 个工作日出具</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>教务/运营</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>是（套餐内）</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>必须可抽查</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
+          <t>「开证明」易引发不实经历质疑，品牌与舆情风险不对等</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>(b) 申报邮箱链接</t>
+          <t>机会成本</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>开通申报邮箱、材料清单、FAQ、进度查询</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>企业邮/表单/知识库</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>提交后 1 个工作日回执</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>客服</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>GW-02 起含</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>可对接机构</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
+          <t>同样教务/企业带宽可售 5,480–11,800 高价值档</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>(c) 推荐信支持</t>
+          <t>战略聚焦</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>结构模板、中英润色、导师签字与用印</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>文档流+电子签</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>材料齐后 5–7 个工作日</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>文书+导师</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>GW-03 含</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>禁止虚假陈述</t>
+          <t>三类人群需求改由真实企业课题满足，证明只作交付物</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>三、公益→商业转化漏斗（目标）</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>三、在售高价值产品（替代组合）</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>阶段</t>
+          <t>产品代码</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>指标</t>
+          <t>产品名称</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>目标值</t>
+          <t>标准价(元)</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>实际值</t>
+          <t>交付物</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>完成率</t>
+          <t>周期</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>主要人群</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>曝光</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>月咨询线索</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>300</v>
-      </c>
-      <c r="D19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="21">
-        <f>IFERROR(D19/C19,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="20" t="inlineStr"/>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>BZ-01</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>科技/具身智能项目实习</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>5480</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>真实课题+周报+结业证明</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>4–6 周</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>高中优生/大学生</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>主推</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>注册</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>公益线报名</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>120</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="21">
-        <f>IFERROR(D20/C20,0)</f>
-        <v/>
-      </c>
-      <c r="F20" s="20" t="inlineStr"/>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>BZ-02</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>上海 AI / 头部通道营</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>11800</v>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>品牌项目+导师+答辩+证明</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>4–6 周</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>大学生优生</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>高毛利</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>完课</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>证明出具数</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="n">
-        <v>100</v>
-      </c>
-      <c r="D21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="21">
-        <f>IFERROR(D21/C21,0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="20" t="inlineStr"/>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>JY-01</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>毕业生就业转化包</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>过渡实习+内推辅导+证明</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>6–12 周</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>毕业生</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>转化出口</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>升级</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>转化商业套餐人数</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="21">
-        <f>IFERROR(D22/C22,0)</f>
-        <v/>
-      </c>
-      <c r="F22" s="20" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>转化率</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>升级/完课</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr"/>
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>ZZ-01</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>推荐信加购（不可单卖）</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>中/英推荐信</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>随项目</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>在营学员</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>四、对外话术红线</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>• 不得再宣传或报价任何「开证明 / 盖章证明 / 低价实习证明」单独产品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>• 结业证明仅作为高价值项目履约交付物，须基于真实课题完成情况出具。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>• 推荐信不得单独售卖；仅可对已参加项目的学员加购，且内容须基于真实表现。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A10:I10"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5861,15 +5763,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -5888,14 +5790,14 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>分层套餐 · 成本加成 · 支付节奏 · 折扣政策</t>
+          <t>仅高价值档 · 成本加成 · 支付节奏 · 折扣政策 · 已取消开证明</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>一、面向 C 端标准价目表</t>
+          <t>一、面向 C 端标准价目表（在售）</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -5973,753 +5875,742 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>公益</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>商业</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>科技/具身智能项目实习</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>3980</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>6980</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>5480</v>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>4–6周真实课题+周报+结业证明</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>包录取/包转正</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>高中优生/大学生</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>4 周</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>定金不退，企业未确认前可协商</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>高校社团</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>商业</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>上海AI/头部通道营</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>8800</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>15800</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>11800</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>品牌项目+导师+答辩+证明</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>包转正</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>大学生/优生</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>4–6 周</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>分期节点退费</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>KOL/机构</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>就业</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>毕业生过渡实习包</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>6800</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>12800</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>9800</v>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>实习+内推辅导+复盘+证明</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>包 Offer</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>毕业生</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>6–12 周</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>入营评估后按阶段退</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>社招渠道</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>增值</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>推荐信加购</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>中/英推荐信（仅项目学员）</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>不可单独购买</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>在营/结业学员</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>随项目</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>启动后不退</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>项目内转化</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>B端</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>学校/教培团购</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>标准价×0.6</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>标准价×0.8</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>按协议</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>批量名额+统一课题交付</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>开证明/造假包装</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>学校/机构</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>按学期</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>合同约定</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>商务BD</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>二、已停售（勿再对外报价）</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="21" t="n"/>
+      <c r="L12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>原套餐</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>原标准价</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>线上实习·证明版</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>299</v>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="B14" s="23" t="n">
         <v>199</v>
       </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>任务+证明编号</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>推荐信/一对一</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>高中生/预算敏感</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>2 周</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>开营后不退，可延期一次</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>社群/学校</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>公益</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>开证明低价档取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>证明+申报支持</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
-        <v>499</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>899</v>
-      </c>
-      <c r="E7" s="14" t="n">
+      <c r="B15" s="23" t="n">
         <v>699</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>证明+邮箱通道+清单</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>推荐信深度润色</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>高中申请</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>2–4 周</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
-        <is>
-          <t>未开通邮箱前可退 80%</t>
-        </is>
-      </c>
-      <c r="K7" s="14" t="inlineStr">
-        <is>
-          <t>留学机构</t>
-        </is>
-      </c>
-      <c r="L7" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>公益</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>开证明低价档取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>证明+推荐信协助</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>1280</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E8" s="11" t="n">
+      <c r="B16" s="23" t="n">
         <v>1680</v>
       </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>模板+润色+签字流</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>包录取</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>海外申请</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>3–6 周</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>文书启动后按进度退</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>留学机构</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>商业</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>科技公司项目实习</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>3980</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>6980</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>5480</v>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>4–6周项目+证明+周报</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>大厂品牌背书</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>大学生</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>4 周</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>定金不退，未开营退学费 70%</t>
-        </is>
-      </c>
-      <c r="K9" s="14" t="inlineStr">
-        <is>
-          <t>高校社团</t>
-        </is>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>商业</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>大厂/500强通道营</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>8800</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>15800</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>11800</v>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>品牌项目+导师+答辩</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>包转正</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>大学生/优生</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>4–6 周</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>分期节点退费</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>KOL/机构</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>就业</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>毕业生过渡实习包</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>6800</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>12800</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>9800</v>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>实习+内推辅导+复盘</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>包 Offer</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>毕业生</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>6–12 周</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
-        <is>
-          <t>入营评估后按阶段退</t>
-        </is>
-      </c>
-      <c r="K11" s="14" t="inlineStr">
-        <is>
-          <t>社招渠道</t>
-        </is>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>B端</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>学校/教培团购</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>标准价×0.6</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>标准价×0.8</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>按协议</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>批量名额+定制证明</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>个性化文书</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>学校/机构</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>按学期</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>合同约定</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>商务BD</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>二、定价公式与机制</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>开证明低价档取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>三、定价公式与机制</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>机制</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>参数/规则</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>示例</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>成本加成</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>学员价 ≥ 通道成本 + 运营分摊 + 目标毛利</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>商业线目标毛利 35–40%</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>通道 3500 → 学员价约 9,000+</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>三维锚点</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>可信度 × 品牌背书 × 辅导强度</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>每维 1–5 分加权</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>S 级品牌+强导师 → 进阶价</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>版本差异</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>基础/标准/精品功能开关</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>证明/申报/推荐信/导师答辩</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>公益三档清晰升级</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>支付节奏</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>定金 30% + 开营 40% + 结业 30%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>与交付物绑定</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>降低纠纷与坏账</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>折扣纪律</t>
+          <t>成本加成</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>早鸟/团购折扣 ≤ 20%</t>
+          <t>学员价 ≥ 通道成本 + 运营分摊 + 目标毛利</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>需审批</t>
+          <t>商业线目标毛利 34–42%</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>保护品牌与单价</t>
+          <t>通道 2400 → 学员价约 5,480</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
+          <t>三维锚点</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>企业品牌 × 课题真实度 × 辅导强度</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>每维 1–5 分加权</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>上海AI头部+强导师 → 进阶价</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>交付绑定</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>结业证明随项目交付，不单卖</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>禁止开证明产品线</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>证明=履约结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>支付节奏</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>定金 30% + 企业确认 40% + 结业 30%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>与交付物绑定</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>降低纠纷与坏账</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>折扣纪律</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>早鸟/团购折扣 ≤ 20%</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>需审批</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>保护品牌与单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>动态调价</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>旺季（寒暑假）上浮 10–15%</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>淡季赠增值不降标价</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>暑假大厂营可上浮</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>三、单人成本拆解（商业标准套餐示意，标准价 5,480）</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>暑假通道营可上浮</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>四、单人成本拆解（商业标准套餐示意，标准价 5,480）</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>成本项</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>金额(元)</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>占比</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>企业通道/课题合作费</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B29" s="29" t="n">
         <v>1800</v>
       </c>
-      <c r="C25" s="21">
-        <f>B25/5480</f>
-        <v/>
-      </c>
-      <c r="D25" s="20" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>导师辅导与批改</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="n">
-        <v>600</v>
-      </c>
-      <c r="C26" s="25">
-        <f>B26/5480</f>
-        <v/>
-      </c>
-      <c r="D26" s="24" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>运营与客服分摊</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n">
-        <v>450</v>
-      </c>
-      <c r="C27" s="21">
-        <f>B27/5480</f>
-        <v/>
-      </c>
-      <c r="D27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>获客 CAC</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="n">
-        <v>900</v>
-      </c>
-      <c r="C28" s="25">
-        <f>B28/5480</f>
-        <v/>
-      </c>
-      <c r="D28" s="24" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>平台与证明/合规</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
-        <v>250</v>
-      </c>
-      <c r="C29" s="21">
+      <c r="C29" s="30">
         <f>B29/5480</f>
         <v/>
       </c>
-      <c r="D29" s="20" t="inlineStr"/>
+      <c r="D29" s="29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>其他/预备费</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="n">
-        <v>200</v>
-      </c>
-      <c r="C30" s="25">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>导师辅导与批改</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="n">
+        <v>600</v>
+      </c>
+      <c r="C30" s="33">
         <f>B30/5480</f>
         <v/>
       </c>
-      <c r="D30" s="24" t="inlineStr"/>
+      <c r="D30" s="32" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>成本合计</t>
-        </is>
-      </c>
-      <c r="B31" s="17">
-        <f>SUM(B25:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="26">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>运营与客服分摊</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="n">
+        <v>450</v>
+      </c>
+      <c r="C31" s="30">
         <f>B31/5480</f>
         <v/>
       </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>毛利 ≈ 标准价 − 成本合计</t>
-        </is>
-      </c>
+      <c r="D31" s="29" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>获客 CAC</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="n">
+        <v>900</v>
+      </c>
+      <c r="C32" s="33">
+        <f>B32/5480</f>
+        <v/>
+      </c>
+      <c r="D32" s="32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>单人毛利(元)</t>
-        </is>
-      </c>
-      <c r="B33" s="27">
-        <f>5480-B31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="27" t="inlineStr">
-        <is>
-          <t>单人毛利率</t>
-        </is>
-      </c>
-      <c r="B34" s="28">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>平台与合规</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>250</v>
+      </c>
+      <c r="C33" s="30">
         <f>B33/5480</f>
         <v/>
       </c>
+      <c r="D33" s="29" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>其他/预备费</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="n">
+        <v>200</v>
+      </c>
+      <c r="C34" s="33">
+        <f>B34/5480</f>
+        <v/>
+      </c>
+      <c r="D34" s="32" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>成本合计</t>
+        </is>
+      </c>
+      <c r="B35" s="17">
+        <f>SUM(B29:B34)</f>
+        <v/>
+      </c>
+      <c r="C35" s="34">
+        <f>B35/5480</f>
+        <v/>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>毛利 ≈ 标准价 − 成本合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>单人毛利(元)</t>
+        </is>
+      </c>
+      <c r="B37" s="35">
+        <f>5480-B35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>单人毛利率</t>
+        </is>
+      </c>
+      <c r="B38" s="36">
+        <f>B37/5480</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A12:L12"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6732,7 +6623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6757,7 +6648,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>可调参数区（改黄色单元格）→ 自动汇总三情景</t>
+          <t>可调参数区（改黄色单元格）→ 自动汇总三情景｜已取消开证明，仅高价值三档</t>
         </is>
       </c>
     </row>
@@ -6810,256 +6701,248 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>付费总人数</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
-        <v>120</v>
-      </c>
-      <c r="C6" s="29" t="n">
-        <v>220</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>360</v>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="B6" s="37" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" s="37" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>300</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>年度或滚动 12 个月</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>公益人数占比</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="n">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>商业标准人数占比</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C7" s="38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="38" t="n">
         <v>0.45</v>
       </c>
-      <c r="C7" s="30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D7" s="30" t="n">
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>科技/具身项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>商业进阶人数占比</t>
+        </is>
+      </c>
+      <c r="B8" s="38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D8" s="38" t="n">
         <v>0.35</v>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>含基础+精品</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>商业人数占比</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C8" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>上海AI/头部通道</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>就业包人数占比</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>标准+进阶</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>就业包人数占比</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C9" s="30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D9" s="30" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>毕业生</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>商业标准客单</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="n">
+        <v>5200</v>
+      </c>
+      <c r="C10" s="37" t="n">
+        <v>5480</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>6200</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>商业进阶客单</t>
+        </is>
+      </c>
+      <c r="B11" s="37" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C11" s="37" t="n">
+        <v>11800</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>就业包客单</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C12" s="37" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D12" s="37" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>综合毛利率</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C13" s="38" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D13" s="38" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>毕业生</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>公益均客单</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>650</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>900</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>证明/申报/推荐信混合</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>商业均客单</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>7200</v>
-      </c>
-      <c r="C11" s="29" t="n">
-        <v>8200</v>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>9500</v>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>标准与进阶混合</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>就业包客单</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>9800</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>综合毛利率</t>
-        </is>
-      </c>
-      <c r="B13" s="30" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="C13" s="30" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="D13" s="30" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>收入结构加权后</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>固定成本</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="n">
+        <v>280000</v>
+      </c>
+      <c r="C14" s="37" t="n">
+        <v>320000</v>
+      </c>
+      <c r="D14" s="37" t="n">
+        <v>380000</v>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>元/年</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>人员+平台+合规+办公</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>获客占收入比</t>
+        </is>
+      </c>
+      <c r="B15" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C15" s="38" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D15" s="38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>收入结构加权后</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>固定成本</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="n">
-        <v>280000</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>320000</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>380000</v>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>人员+平台+合规+办公</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>获客占收入比</t>
-        </is>
-      </c>
-      <c r="B15" s="30" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C15" s="30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D15" s="30" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>渠道与内容投放</t>
         </is>
@@ -7109,72 +6992,72 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>公益人数</t>
-        </is>
-      </c>
-      <c r="B19" s="14">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>商业标准人数</t>
+        </is>
+      </c>
+      <c r="B19" s="11">
         <f>ROUND(B6*B7,0)</f>
         <v/>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="11">
         <f>ROUND(C6*C7,0)</f>
         <v/>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="11">
         <f>ROUND(D6*D7,0)</f>
         <v/>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>总人数×公益占比</t>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>总人数×标准占比</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>商业人数</t>
-        </is>
-      </c>
-      <c r="B20" s="11">
+          <t>商业进阶人数</t>
+        </is>
+      </c>
+      <c r="B20" s="14">
         <f>ROUND(B6*B8,0)</f>
         <v/>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="14">
         <f>ROUND(C6*C8,0)</f>
         <v/>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="14">
         <f>ROUND(D6*D8,0)</f>
         <v/>
       </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>总人数×商业占比</t>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>总人数×进阶占比</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>就业包人数</t>
         </is>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="11">
         <f>ROUND(B6*B9,0)</f>
         <v/>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="11">
         <f>ROUND(C6*C9,0)</f>
         <v/>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="11">
         <f>ROUND(D6*D9,0)</f>
         <v/>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>总人数×就业占比</t>
         </is>
@@ -7183,46 +7066,46 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>公益收入(元)</t>
-        </is>
-      </c>
-      <c r="B22" s="32">
+          <t>标准收入(元)</t>
+        </is>
+      </c>
+      <c r="B22" s="40">
         <f>B19*B10</f>
         <v/>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="40">
         <f>C19*C10</f>
         <v/>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="40">
         <f>D19*D10</f>
         <v/>
       </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>人数×均客单</t>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>人数×客单</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>商业收入(元)</t>
-        </is>
-      </c>
-      <c r="B23" s="33">
+      <c r="A23" s="39" t="inlineStr">
+        <is>
+          <t>进阶收入(元)</t>
+        </is>
+      </c>
+      <c r="B23" s="41">
         <f>B20*B11</f>
         <v/>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="41">
         <f>C20*C11</f>
         <v/>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="41">
         <f>D20*D11</f>
         <v/>
       </c>
-      <c r="E23" s="14" t="inlineStr"/>
+      <c r="E23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -7230,39 +7113,39 @@
           <t>就业收入(元)</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="40">
         <f>B21*B12</f>
         <v/>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="40">
         <f>C21*C12</f>
         <v/>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="40">
         <f>D21*D12</f>
         <v/>
       </c>
-      <c r="E24" s="11" t="inlineStr"/>
+      <c r="E24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>总营收(元)</t>
         </is>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="41">
         <f>B22+B23+B24</f>
         <v/>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="41">
         <f>C22+C23+C24</f>
         <v/>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="41">
         <f>D22+D23+D24</f>
         <v/>
       </c>
-      <c r="E25" s="14" t="inlineStr"/>
+      <c r="E25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -7270,39 +7153,39 @@
           <t>总营收(万元)</t>
         </is>
       </c>
-      <c r="B26" s="34">
+      <c r="B26" s="42">
         <f>B25/10000</f>
         <v/>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="42">
         <f>C25/10000</f>
         <v/>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="42">
         <f>D25/10000</f>
         <v/>
       </c>
-      <c r="E26" s="11" t="inlineStr"/>
+      <c r="E26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="39" t="inlineStr">
         <is>
           <t>毛利(元)</t>
         </is>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="41">
         <f>B25*B13</f>
         <v/>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="41">
         <f>C25*C13</f>
         <v/>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="41">
         <f>D25*D13</f>
         <v/>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>营收×综合毛利率</t>
         </is>
@@ -7314,83 +7197,83 @@
           <t>毛利(万元)</t>
         </is>
       </c>
-      <c r="B28" s="34">
+      <c r="B28" s="42">
         <f>B27/10000</f>
         <v/>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="42">
         <f>C27/10000</f>
         <v/>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="42">
         <f>D27/10000</f>
         <v/>
       </c>
-      <c r="E28" s="11" t="inlineStr"/>
+      <c r="E28" s="14" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>固定成本(元)</t>
         </is>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="41">
         <f>B14</f>
         <v/>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="41">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="41">
         <f>D14</f>
         <v/>
       </c>
-      <c r="E29" s="14" t="inlineStr"/>
+      <c r="E29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>经营盈余(元)</t>
         </is>
       </c>
-      <c r="B30" s="36">
+      <c r="B30" s="44">
         <f>B27-B29</f>
         <v/>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="44">
         <f>C27-C29</f>
         <v/>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="44">
         <f>D27-D29</f>
         <v/>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>毛利−固定成本</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="43" t="inlineStr">
         <is>
           <t>经营盈余(万元)</t>
         </is>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="45">
         <f>B30/10000</f>
         <v/>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="45">
         <f>C30/10000</f>
         <v/>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="45">
         <f>D30/10000</f>
         <v/>
       </c>
-      <c r="E31" s="14" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -7398,19 +7281,19 @@
           <t>是否盈亏平衡</t>
         </is>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="14">
         <f>IF(B30&gt;=0,"是","否")</f>
         <v/>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="14">
         <f>IF(C30&gt;=0,"是","否")</f>
         <v/>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="14">
         <f>IF(D30&gt;=0,"是","否")</f>
         <v/>
       </c>
-      <c r="E32" s="11" t="inlineStr"/>
+      <c r="E32" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -7497,7 +7380,7 @@
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>公益→商业转化不足</t>
+          <t>标准→进阶升级不足</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -7512,7 +7395,7 @@
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>完课后 7 日内升级优惠（≤15%）</t>
+          <t>结业前 7 日内升级优惠（≤15%）</t>
         </is>
       </c>
     </row>
@@ -7557,6 +7440,28 @@
       <c r="D40" s="19" t="inlineStr">
         <is>
           <t>每赛道 ≥2 家备份</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>重回低价开证明</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>风险回潮</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>是否出现违规报价</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>价目表审计；违者下架</t>
         </is>
       </c>
     </row>
@@ -7676,496 +7581,492 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>基建</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>产品三档封装与话术</t>
+          <t>高价值三档产品封装与话术</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>产品说明书</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr">
+          <t>产品说明书（无开证明）</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr"/>
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="14" t="inlineStr"/>
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr"/>
+      <c r="I6" s="14" t="inlineStr"/>
+      <c r="J6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>基建</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>实习证明模板与编号规则</t>
+          <t>下架开证明相关页面/报价</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>证明模板 V1</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr"/>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr">
+          <t>停售确认清单</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>199/699/1680</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>基建</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>报名表单/收款/协议</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>电子协议+表单</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr"/>
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr"/>
-      <c r="J7" s="14" t="inlineStr">
-        <is>
-          <t>合规法务过目</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr"/>
+      <c r="J8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>供给</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>签约上海AI/具身 5–8 家</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>合作意向/协议</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="11" t="inlineStr"/>
+      <c r="G9" s="11" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>基建</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>报名表单/收款/协议</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>电子协议+表单</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr"/>
-      <c r="G8" s="11" t="inlineStr"/>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>供给</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>组建导师池 ≥ 10 人</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>导师名单</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="11" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr"/>
+      <c r="J10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>供给</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>签约 SaaS/科技公司 5–8 家</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>合作意向/协议</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="14" t="inlineStr"/>
-      <c r="G9" s="14" t="inlineStr"/>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>确认 AI 头部通道 1–2 条</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>通道说明</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="11" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr"/>
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>获客</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>高校社团/机构渠道试点</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>渠道清单</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>获客</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>商业标准档首批开营</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>30 人开营</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr"/>
+      <c r="G13" s="11" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>供给</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>组建导师池 ≥ 10 人</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>导师名单</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr"/>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>进阶通道营开营</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>案例与口碑</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="14" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="11" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>标准→进阶升级追踪</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>升级率报表</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>转化</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>毕业生就业包上线</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>产品页+辅导流程</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
+      <c r="G16" s="14" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>供给</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>确认大厂通道 1–2 条试点</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>通道说明</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
-      <c r="G11" s="14" t="inlineStr"/>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>转化</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Offer/升学反馈收集</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>案例 ≥10</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr"/>
+      <c r="G17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr"/>
-      <c r="J11" s="14" t="inlineStr">
-        <is>
-          <t>可先用合作课题</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>获客</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>留学机构/高校社团渠道试点</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>渠道清单</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr"/>
-      <c r="F12" s="11" t="inlineStr"/>
-      <c r="G12" s="11" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>复盘</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>财务与 NPS 复盘</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>复盘报告</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>获客</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>公益线首批开营</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>40 人开营</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
-      <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>复盘</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>是否扩张决策会</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Go/No-Go 纪要</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr"/>
+      <c r="G19" s="11" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>商业标准营开营</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>案例与口碑</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr"/>
-      <c r="F14" s="11" t="inlineStr"/>
-      <c r="G14" s="11" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>大厂/进阶营首期</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>结业答辩录像</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
-      <c r="G15" s="14" t="inlineStr"/>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>转化</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>毕业生就业包上线</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>产品页+辅导流程</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr"/>
-      <c r="G16" s="11" t="inlineStr"/>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>转化</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Offer/升学反馈收集</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>案例 ≥10</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
-      <c r="G17" s="14" t="inlineStr"/>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>复盘</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>财务与 NPS 复盘</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>复盘报告</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr"/>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>全部</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>复盘</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>是否扩张决策会</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Go/No-Go 纪要</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr"/>
-      <c r="F19" s="14" t="inlineStr"/>
-      <c r="G19" s="14" t="inlineStr"/>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>复盘报告</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8279,7 +8180,7 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>R01</t>
         </is>
@@ -8289,22 +8190,22 @@
           <t>出具不实实习证明引发投诉/舆情</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>合规</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F6" s="38" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8314,15 +8215,15 @@
           <t>真实任务+编号核验+抽查+拒绝虚假需求</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr"/>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>R02</t>
         </is>
@@ -8332,22 +8233,22 @@
           <t>企业合作中断导致无法交付</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>供给</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F7" s="38" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8357,15 +8258,15 @@
           <t>每赛道≥2备份；合同约定替补方案</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr"/>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>R03</t>
         </is>
@@ -8375,22 +8276,22 @@
           <t>价格战与「水项目」冲击</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F8" s="38" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8400,15 +8301,15 @@
           <t>强化可核验与成果物；案例与 NPS 公开</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr"/>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>R04</t>
         </is>
@@ -8418,22 +8319,22 @@
           <t>退费与消费纠纷</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>运营</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -8443,15 +8344,15 @@
           <t>分期交付、书面协议、补学/延期机制</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr"/>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>R05</t>
         </is>
@@ -8461,22 +8362,22 @@
           <t>未成年人信息与监护人同意缺失</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>合规</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F10" s="38" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8486,15 +8387,15 @@
           <t>隐私告知书+监护人同意；最小必要采集</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr"/>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>R06</t>
         </is>
@@ -8504,22 +8405,22 @@
           <t>推荐信/文书虚假陈述</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>合规</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F11" s="38" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8529,15 +8430,15 @@
           <t>仅基于真实表现；审核清单；拒绝包装造假</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
@@ -8547,22 +8448,22 @@
           <t>品牌方名称使用不当</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>法务</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F12" s="38" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8572,15 +8473,15 @@
           <t>对外话术经法务审核；避免虚假「官方实习」表述</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr"/>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>R08</t>
         </is>
@@ -8590,22 +8491,22 @@
           <t>获客成本失控</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>财务</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -8615,51 +8516,51 @@
           <t>周度 CAC 看板；达标渠道加码，未达标停投</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>对外话术红线（摘要）</t>
         </is>
       </c>
-      <c r="B15" s="40" t="n"/>
-      <c r="C15" s="40" t="n"/>
-      <c r="D15" s="40" t="n"/>
-      <c r="E15" s="40" t="n"/>
-      <c r="F15" s="40" t="n"/>
-      <c r="G15" s="40" t="n"/>
-      <c r="H15" s="40" t="n"/>
-      <c r="I15" s="40" t="n"/>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="26" t="n"/>
+      <c r="G15" s="26" t="n"/>
+      <c r="H15" s="26" t="n"/>
+      <c r="I15" s="26" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="41" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>• 不得承诺「包录取 / 包 Offer / 包进某公司正式编制」。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>• 涉及知名企业时，须准确表述合作形态（联合课题/合作方项目/导师来自生态等），禁止虚假「官方实习生」宣传。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>• 证明内容必须与学员真实完成的任务一致，保留过程材料备查。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>• 推荐信仅描述可验证事实与导师真实评价。</t>
         </is>
